--- a/data/trans_dic/P04D$individual-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P04D$individual-Habitat-trans_dic.xlsx
@@ -524,7 +524,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que, al menos, tiene calefacción individual en su vivienda</t>
+          <t>Población que, al menos, tiene calefacción individual en su vivienda (tasa de respuesta: 99,87%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>21,92; 28,69</t>
+          <t>21,92; 28,81</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>23,0; 29,63</t>
+          <t>22,79; 29,73</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>12,66; 20,14</t>
+          <t>12,68; 20,8</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>22,35; 29,0</t>
+          <t>22,0; 28,61</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>22,11; 28,87</t>
+          <t>21,58; 28,14</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>11,57; 17,53</t>
+          <t>11,43; 17,48</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>23,1; 27,75</t>
+          <t>22,98; 27,76</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>23,29; 27,89</t>
+          <t>23,25; 28,08</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>13,1; 17,73</t>
+          <t>13,23; 17,84</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>24,46; 30,34</t>
+          <t>24,72; 30,42</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>24,25; 30,14</t>
+          <t>24,41; 30,34</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>19,37; 65,72</t>
+          <t>19,36; 70,96</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>22,61; 28,2</t>
+          <t>22,52; 28,01</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>25,8; 31,65</t>
+          <t>26,18; 31,78</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>13,62; 17,93</t>
+          <t>13,43; 17,68</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>24,26; 28,47</t>
+          <t>24,2; 28,43</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>25,85; 30,06</t>
+          <t>25,99; 30,24</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>17,38; 50,36</t>
+          <t>17,35; 52,5</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>21,51; 28,38</t>
+          <t>21,58; 28,44</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>30,92; 38,46</t>
+          <t>31,06; 38,09</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>7,9; 12,55</t>
+          <t>7,74; 12,42</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>18,93; 25,2</t>
+          <t>18,62; 24,78</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>33,97; 41,14</t>
+          <t>34,31; 41,17</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>3,48; 9,77</t>
+          <t>3,64; 9,7</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>21,32; 25,75</t>
+          <t>21,24; 25,78</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>33,71; 38,71</t>
+          <t>33,55; 38,63</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>5,42; 10,15</t>
+          <t>5,51; 10,17</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>36,16; 42,97</t>
+          <t>36,25; 42,76</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>23,86; 29,5</t>
+          <t>24,02; 29,88</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>21,19; 27,35</t>
+          <t>21,23; 27,27</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>34,76; 40,8</t>
+          <t>34,77; 40,87</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>28,68; 34,79</t>
+          <t>28,83; 34,89</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>17,37; 25,37</t>
+          <t>17,93; 25,44</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>36,15; 40,78</t>
+          <t>36,26; 40,78</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>27,28; 31,41</t>
+          <t>27,25; 31,69</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>20,82; 25,44</t>
+          <t>20,66; 25,48</t>
         </is>
       </c>
     </row>
@@ -1118,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>28,3; 31,41</t>
+          <t>28,11; 31,42</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>26,91; 30,21</t>
+          <t>27,03; 30,17</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>17,81; 42,85</t>
+          <t>17,86; 42,2</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>26,82; 29,97</t>
+          <t>26,82; 29,74</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>29,27; 32,61</t>
+          <t>29,22; 32,39</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>12,5; 16,91</t>
+          <t>12,48; 16,79</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>27,9; 30,17</t>
+          <t>27,88; 30,06</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>28,57; 30,91</t>
+          <t>28,63; 30,88</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>16,37; 30,53</t>
+          <t>16,14; 29,59</t>
         </is>
       </c>
     </row>
@@ -1210,7 +1210,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que, al menos, tiene calefacción individual en su vivienda</t>
+          <t>Población que, al menos, tiene calefacción individual en su vivienda (tasa de respuesta: 99,87%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1417,47 +1417,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>153601; 201010</t>
+          <t>153609; 201865</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>155197; 199968</t>
+          <t>153765; 200644</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>80203; 127587</t>
+          <t>80345; 131755</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>155522; 201816</t>
+          <t>153070; 199119</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>148733; 194224</t>
+          <t>145216; 189330</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>83873; 127056</t>
+          <t>82828; 126707</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>322679; 387570</t>
+          <t>320983; 387663</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>313849; 375818</t>
+          <t>313275; 378484</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>177919; 240768</t>
+          <t>179685; 242277</t>
         </is>
       </c>
     </row>
@@ -1580,47 +1580,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>248174; 307775</t>
+          <t>250790; 308622</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>247951; 308210</t>
+          <t>249542; 310193</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>230887; 783289</t>
+          <t>230800; 845713</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>232940; 290533</t>
+          <t>231993; 288483</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>269113; 330110</t>
+          <t>273018; 331400</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>130276; 171443</t>
+          <t>128467; 169102</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>496008; 582038</t>
+          <t>494750; 581371</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>533821; 620801</t>
+          <t>536808; 624469</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>373304; 1081866</t>
+          <t>372655; 1127849</t>
         </is>
       </c>
     </row>
@@ -1743,47 +1743,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>162753; 214770</t>
+          <t>163321; 215232</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>234856; 292119</t>
+          <t>235915; 289304</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>55569; 88305</t>
+          <t>54428; 87363</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>146909; 195621</t>
+          <t>144507; 192331</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>266693; 322978</t>
+          <t>269339; 323206</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>32399; 90968</t>
+          <t>33923; 90319</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>326737; 394675</t>
+          <t>325612; 395221</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>520640; 597877</t>
+          <t>518243; 596674</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>88593; 165883</t>
+          <t>90074; 166248</t>
         </is>
       </c>
     </row>
@@ -1906,47 +1906,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>342730; 407218</t>
+          <t>343509; 405238</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>223718; 276573</t>
+          <t>225191; 280113</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>195928; 252918</t>
+          <t>196332; 252193</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>365611; 429211</t>
+          <t>365785; 429888</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>299351; 363135</t>
+          <t>300890; 364132</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>189689; 276973</t>
+          <t>195794; 277763</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>722913; 815400</t>
+          <t>724989; 815516</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>540562; 622363</t>
+          <t>539956; 627982</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>419913; 512956</t>
+          <t>416645; 513760</t>
         </is>
       </c>
     </row>
@@ -2069,47 +2069,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>967788; 1074169</t>
+          <t>961210; 1074530</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>913455; 1025358</t>
+          <t>917657; 1024029</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>615159; 1480020</t>
+          <t>616833; 1457534</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>953284; 1065229</t>
+          <t>953120; 1056955</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>1037651; 1155967</t>
+          <t>1035693; 1148130</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>462986; 626384</t>
+          <t>462330; 621803</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>1946023; 2104058</t>
+          <t>1944460; 2096331</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>1982149; 2144756</t>
+          <t>1986461; 2142806</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>1172093; 2185682</t>
+          <t>1155383; 2117910</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P04D$individual-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P04D$individual-Habitat-trans_dic.xlsx
@@ -635,7 +635,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>15,78%</t>
+          <t>15,67%</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -650,7 +650,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>14,92%</t>
+          <t>15,62%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -665,7 +665,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>15,32%</t>
+          <t>15,64%</t>
         </is>
       </c>
     </row>
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>21,92; 28,81</t>
+          <t>22,14; 29,01</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>22,79; 29,73</t>
+          <t>22,87; 29,57</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>12,68; 20,8</t>
+          <t>12,51; 19,47</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>22,0; 28,61</t>
+          <t>22,28; 28,69</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>21,58; 28,14</t>
+          <t>22,01; 28,63</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>11,43; 17,48</t>
+          <t>13,26; 17,91</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>22,98; 27,76</t>
+          <t>23,05; 27,68</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>23,25; 28,08</t>
+          <t>23,0; 28,03</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>13,23; 17,84</t>
+          <t>13,84; 17,78</t>
         </is>
       </c>
     </row>
@@ -745,7 +745,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>36,64%</t>
+          <t>19,8%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>15,42%</t>
+          <t>15,06%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -775,7 +775,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>27,19%</t>
+          <t>17,41%</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>24,72; 30,42</t>
+          <t>24,65; 30,41</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>24,41; 30,34</t>
+          <t>24,46; 30,07</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>19,36; 70,96</t>
+          <t>16,93; 22,72</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>22,52; 28,01</t>
+          <t>22,72; 28,28</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>26,18; 31,78</t>
+          <t>26,19; 31,81</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>13,43; 17,68</t>
+          <t>13,13; 17,18</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>24,2; 28,43</t>
+          <t>24,6; 28,65</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>25,99; 30,24</t>
+          <t>25,98; 30,12</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>17,35; 52,5</t>
+          <t>15,8; 19,32</t>
         </is>
       </c>
     </row>
@@ -855,7 +855,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>9,99%</t>
+          <t>10,14%</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -870,7 +870,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>7,0%</t>
+          <t>9,4%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -885,7 +885,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>8,29%</t>
+          <t>9,77%</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>21,58; 28,44</t>
+          <t>21,48; 28,22</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>31,06; 38,09</t>
+          <t>30,99; 38,07</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>7,74; 12,42</t>
+          <t>7,75; 12,74</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>18,62; 24,78</t>
+          <t>19,04; 25,36</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>34,31; 41,17</t>
+          <t>33,85; 41,03</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>3,64; 9,7</t>
+          <t>7,74; 11,3</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>21,24; 25,78</t>
+          <t>21,19; 25,59</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>33,55; 38,63</t>
+          <t>33,71; 38,83</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>5,51; 10,17</t>
+          <t>8,46; 11,27</t>
         </is>
       </c>
     </row>
@@ -965,7 +965,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>24,09%</t>
+          <t>23,48%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -980,7 +980,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>22,63%</t>
+          <t>24,05%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -995,7 +995,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>23,3%</t>
+          <t>23,79%</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>36,25; 42,76</t>
+          <t>36,1; 42,44</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>24,02; 29,88</t>
+          <t>23,93; 29,85</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>21,23; 27,27</t>
+          <t>20,5; 26,4</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>34,77; 40,87</t>
+          <t>34,85; 41,07</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>28,83; 34,89</t>
+          <t>28,49; 34,53</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>17,93; 25,44</t>
+          <t>21,62; 26,6</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>36,26; 40,78</t>
+          <t>36,31; 40,58</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>27,25; 31,69</t>
+          <t>27,33; 31,57</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>20,66; 25,48</t>
+          <t>22,13; 25,64</t>
         </is>
       </c>
     </row>
@@ -1075,7 +1075,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>24,02%</t>
+          <t>17,84%</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>15,33%</t>
+          <t>16,63%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1105,7 +1105,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>19,53%</t>
+          <t>17,22%</t>
         </is>
       </c>
     </row>
@@ -1118,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>28,11; 31,42</t>
+          <t>28,16; 31,38</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>27,03; 30,17</t>
+          <t>26,99; 30,25</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>17,86; 42,2</t>
+          <t>16,47; 19,43</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>26,82; 29,74</t>
+          <t>26,77; 29,71</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>29,22; 32,39</t>
+          <t>29,4; 32,68</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>12,48; 16,79</t>
+          <t>15,55; 17,83</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>27,88; 30,06</t>
+          <t>27,96; 30,2</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>28,63; 30,88</t>
+          <t>28,61; 30,87</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>16,14; 29,59</t>
+          <t>16,35; 18,14</t>
         </is>
       </c>
     </row>
@@ -1374,7 +1374,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>99928</t>
+          <t>107877</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1389,7 +1389,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>108142</t>
+          <t>114561</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>208070</t>
+          <t>222438</t>
         </is>
       </c>
     </row>
@@ -1417,47 +1417,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>153609; 201865</t>
+          <t>155158; 203291</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>153765; 200644</t>
+          <t>154312; 199522</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>80345; 131755</t>
+          <t>86112; 134038</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>153070; 199119</t>
+          <t>155036; 199660</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>145216; 189330</t>
+          <t>148115; 192613</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>82828; 126707</t>
+          <t>97292; 131378</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>320983; 387663</t>
+          <t>321962; 386636</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>313275; 378484</t>
+          <t>310002; 377709</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>179685; 242277</t>
+          <t>196752; 252876</t>
         </is>
       </c>
     </row>
@@ -1537,7 +1537,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>436687</t>
+          <t>207444</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -1552,7 +1552,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>147464</t>
+          <t>160870</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1567,7 +1567,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>584152</t>
+          <t>368314</t>
         </is>
       </c>
     </row>
@@ -1580,47 +1580,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>250790; 308622</t>
+          <t>250042; 308538</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>249542; 310193</t>
+          <t>250133; 307474</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>230800; 845713</t>
+          <t>177382; 238005</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>231993; 288483</t>
+          <t>234026; 291316</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>273018; 331400</t>
+          <t>273137; 331721</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>128467; 169102</t>
+          <t>140226; 183505</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>494750; 581371</t>
+          <t>503020; 585879</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>536808; 624469</t>
+          <t>536482; 622047</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>372655; 1127849</t>
+          <t>334269; 408687</t>
         </is>
       </c>
     </row>
@@ -1700,7 +1700,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>70294</t>
+          <t>80869</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1715,7 +1715,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>65178</t>
+          <t>76152</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1730,7 +1730,7 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>135471</t>
+          <t>157021</t>
         </is>
       </c>
     </row>
@@ -1743,47 +1743,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>163321; 215232</t>
+          <t>162541; 213553</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>235915; 289304</t>
+          <t>235418; 289168</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>54428; 87363</t>
+          <t>61820; 101635</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>144507; 192331</t>
+          <t>147800; 196856</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>269339; 323206</t>
+          <t>265748; 322123</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>33923; 90319</t>
+          <t>62675; 91549</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>325612; 395221</t>
+          <t>324841; 392319</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>518243; 596674</t>
+          <t>520683; 599791</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>90074; 166248</t>
+          <t>136073; 181250</t>
         </is>
       </c>
     </row>
@@ -1863,7 +1863,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>222798</t>
+          <t>232001</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1878,7 +1878,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>247155</t>
+          <t>268443</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1893,7 +1893,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>469953</t>
+          <t>500444</t>
         </is>
       </c>
     </row>
@@ -1906,47 +1906,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>343509; 405238</t>
+          <t>342099; 402221</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>225191; 280113</t>
+          <t>224339; 279896</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>196332; 252193</t>
+          <t>202523; 260813</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>365785; 429888</t>
+          <t>366636; 431965</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>300890; 364132</t>
+          <t>297382; 360425</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>195794; 277763</t>
+          <t>241240; 296905</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>724989; 815516</t>
+          <t>726152; 811360</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>539956; 627982</t>
+          <t>541461; 625433</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>416645; 513760</t>
+          <t>465638; 539454</t>
         </is>
       </c>
     </row>
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>829707</t>
+          <t>628191</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -2041,7 +2041,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>567939</t>
+          <t>620026</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2056,7 +2056,7 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>1397646</t>
+          <t>1248217</t>
         </is>
       </c>
     </row>
@@ -2069,47 +2069,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>961210; 1074530</t>
+          <t>962831; 1073187</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>917657; 1024029</t>
+          <t>916057; 1026634</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>616833; 1457534</t>
+          <t>580015; 684328</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>953120; 1056955</t>
+          <t>951445; 1055961</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>1035693; 1148130</t>
+          <t>1041940; 1158477</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>462330; 621803</t>
+          <t>579647; 664506</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>1944460; 2096331</t>
+          <t>1950028; 2105918</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>1986461; 2142806</t>
+          <t>1984874; 2142094</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>1155383; 2117910</t>
+          <t>1185152; 1315414</t>
         </is>
       </c>
     </row>
